--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484781_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484781_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7091</v>
+        <v>7.6107</v>
       </c>
       <c r="E2" t="n">
-        <v>7.935</v>
+        <v>8.598599999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.226</v>
+        <v>-0.9879</v>
       </c>
       <c r="G2" t="n">
         <v>6.5242</v>
@@ -610,13 +610,13 @@
         <v>2.8305</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7283</v>
+        <v>-0.8266</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1975</v>
+        <v>-0.534</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.2927</v>
       </c>
       <c r="V2" t="n">
         <v>0.9696</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.765</v>
+        <v>4.1471</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4097</v>
+        <v>3.5273</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3552</v>
+        <v>0.6198</v>
       </c>
       <c r="G3" t="n">
         <v>0.8458</v>
@@ -688,13 +688,13 @@
         <v>2.0757</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1075</v>
+        <v>-0.7254</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5603</v>
+        <v>-0.4427</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5472</v>
+        <v>-0.2827</v>
       </c>
       <c r="V3" t="n">
         <v>1.9509</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7053</v>
+        <v>1.764</v>
       </c>
       <c r="E4" t="n">
-        <v>3.823</v>
+        <v>3.8818</v>
       </c>
       <c r="F4" t="n">
         <v>-2.1177</v>
@@ -766,10 +766,10 @@
         <v>2.4531</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8847</v>
+        <v>-0.8259</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6191</v>
+        <v>-0.5603</v>
       </c>
       <c r="U4" t="n">
         <v>-0.2656</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8143</v>
+        <v>0.9357</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8943</v>
+        <v>-0.6407</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7086</v>
+        <v>1.5764</v>
       </c>
       <c r="G5" t="n">
         <v>-0.9161</v>
@@ -844,13 +844,13 @@
         <v>0.9435</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1375</v>
+        <v>-0.0161</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3404</v>
+        <v>-0.0867</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2029</v>
+        <v>0.0706</v>
       </c>
       <c r="V5" t="n">
         <v>0.9244</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5309</v>
+        <v>-0.0058</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9308</v>
+        <v>2.6587</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.4</v>
+        <v>-2.6645</v>
       </c>
       <c r="G6" t="n">
         <v>1.8337</v>
@@ -922,13 +922,13 @@
         <v>1.5096</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2816</v>
+        <v>-0.2551</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0617</v>
+        <v>-0.2105</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2199</v>
+        <v>-0.0446</v>
       </c>
       <c r="V6" t="n">
         <v>-3.094</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9254</v>
+        <v>-1.6252</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5657</v>
+        <v>0.8395</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4911</v>
+        <v>-2.4647</v>
       </c>
       <c r="G8" t="n">
         <v>0.9417</v>
@@ -1078,13 +1078,13 @@
         <v>0.7548</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-0.2729</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3281</v>
+        <v>-0.0543</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2451</v>
+        <v>-0.2186</v>
       </c>
       <c r="V8" t="n">
         <v>-3.0488</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9348</v>
+        <v>-2.3413</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4421</v>
+        <v>-0.637</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4926</v>
+        <v>-1.7043</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2656</v>
@@ -1156,13 +1156,13 @@
         <v>1.3209</v>
       </c>
       <c r="S9" t="n">
-        <v>0.425</v>
+        <v>0.0185</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1451</v>
+        <v>-0.0497</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2799</v>
+        <v>0.0682</v>
       </c>
       <c r="V9" t="n">
         <v>-1.528</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9005</v>
+        <v>-3.8397</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1586</v>
+        <v>-2.1771</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.742</v>
+        <v>-1.6626</v>
       </c>
       <c r="G10" t="n">
         <v>-3.4402</v>
@@ -1234,13 +1234,13 @@
         <v>3.0192</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9958</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4304</v>
+        <v>-0.4489</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5654</v>
+        <v>-0.4861</v>
       </c>
       <c r="V10" t="n">
         <v>2.2338</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>5.6825</v>
+        <v>6.5641</v>
       </c>
       <c r="E11" t="n">
-        <v>15.1104</v>
+        <v>15.9923</v>
       </c>
       <c r="F11" t="n">
-        <v>-9.4282</v>
+        <v>-9.428100000000001</v>
       </c>
       <c r="G11" t="n">
         <v>6.9319</v>
@@ -1312,13 +1312,13 @@
         <v>15.096</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.7791</v>
+        <v>-3.8973</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.3278</v>
+        <v>-2.4459</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.4513</v>
+        <v>-1.4515</v>
       </c>
       <c r="V11" t="n">
         <v>-3.075</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.4722</v>
+        <v>6.2406</v>
       </c>
       <c r="E12" t="n">
-        <v>9.311500000000001</v>
+        <v>9.214</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.8393</v>
+        <v>-2.9734</v>
       </c>
       <c r="G12" t="n">
         <v>0.3317</v>
@@ -1390,13 +1390,13 @@
         <v>1.1322</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2274</v>
+        <v>0.9959</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3832</v>
+        <v>0.2858</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1557</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>3.7808</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>W. LADSON BUGALLO</t>
+          <t>P. TORMO HERRERO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.9402</v>
+        <v>1.2953</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7127</v>
+        <v>0.9002</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2275</v>
+        <v>0.3952</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3586</v>
+        <v>2.1854</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1816</v>
+        <v>-3.0858</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.177</v>
+        <v>5.2712</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4481</v>
+        <v>3.2753</v>
       </c>
       <c r="K13" t="n">
-        <v>2.1928</v>
+        <v>-1.8008</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2553</v>
+        <v>5.076</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.8067</v>
+        <v>-1.0899</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.3744</v>
+        <v>-1.285</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4323</v>
+        <v>0.1951</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.5661</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.887</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3209</v>
+        <v>0.9435</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1215</v>
+        <v>0.3101</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8687</v>
+        <v>-0.1673</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2528</v>
+        <v>0.4774</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2566</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2828</v>
+        <v>-0.3208</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5395</v>
+        <v>0.06419999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. TORMO HERRERO</t>
+          <t>D. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5303</v>
+        <v>0.7531</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3156</v>
+        <v>0.5584</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2147</v>
+        <v>0.1946</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1854</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.0858</v>
+        <v>-2.5489</v>
       </c>
       <c r="I14" t="n">
-        <v>5.2712</v>
+        <v>2.6388</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2753</v>
+        <v>1.8568</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.8008</v>
+        <v>-0.7599</v>
       </c>
       <c r="L14" t="n">
-        <v>5.076</v>
+        <v>2.6168</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0899</v>
+        <v>-1.7669</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.285</v>
+        <v>-1.789</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1951</v>
+        <v>0.0221</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9435</v>
+        <v>-1.6983</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.887</v>
+        <v>-2.8305</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9435</v>
+        <v>1.1322</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.455</v>
+        <v>1.0331</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7519</v>
+        <v>0.3059</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2969</v>
+        <v>0.7272</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2566</v>
+        <v>1.3283</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3208</v>
+        <v>1.2262</v>
       </c>
       <c r="X14" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.1021</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. FELIZ CAMEAU</t>
+          <t>W. LADSON BUGALLO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4428</v>
+        <v>0.6872</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0319</v>
+        <v>1.1281</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.589</v>
+        <v>-0.4409</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9667</v>
+        <v>-0.3586</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0485</v>
+        <v>-0.1816</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.0152</v>
+        <v>-0.177</v>
       </c>
       <c r="J15" t="n">
-        <v>1.838</v>
+        <v>2.4481</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0565</v>
+        <v>2.1928</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7815</v>
+        <v>0.2553</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.8047</v>
+        <v>-2.8067</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.008</v>
+        <v>-2.3744</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.7967</v>
+        <v>-0.4323</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9435</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9435</v>
+        <v>1.3209</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7112</v>
+        <v>1.8685</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1939</v>
+        <v>0.2841</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5173</v>
+        <v>1.5844</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2452</v>
+        <v>-0.2566</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.2828</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2452</v>
+        <v>-0.5395</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. HOLGADO CUELLAR</t>
+          <t>O. KOVAL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2649</v>
+        <v>-0.1033</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7533</v>
+        <v>0.4685</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4885</v>
+        <v>-0.5718</v>
       </c>
       <c r="G16" t="n">
-        <v>0.08989999999999999</v>
+        <v>-0.6202</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.5489</v>
+        <v>-0.3107</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6388</v>
+        <v>-0.3095</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8568</v>
+        <v>0.1868</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7599</v>
+        <v>0.0634</v>
       </c>
       <c r="L16" t="n">
-        <v>2.6168</v>
+        <v>0.1234</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7669</v>
+        <v>-0.8069</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.789</v>
+        <v>-0.3741</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0221</v>
+        <v>-0.4329</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.6983</v>
+        <v>0.1887</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1322</v>
+        <v>0.1887</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5449000000000001</v>
+        <v>0.0263</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5008</v>
+        <v>-0.0201</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0441</v>
+        <v>0.0465</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3283</v>
+        <v>0.3018</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2262</v>
+        <v>0.3018</v>
       </c>
       <c r="X16" t="n">
-        <v>0.1021</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. KOVAL</t>
+          <t>N. FELIZ CAMEAU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4365</v>
+        <v>-0.345</v>
       </c>
       <c r="E17" t="n">
-        <v>0.371</v>
+        <v>2.3498</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8075</v>
+        <v>-2.6948</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6202</v>
+        <v>-0.9667</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3107</v>
+        <v>0.0485</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3095</v>
+        <v>-1.0152</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1868</v>
+        <v>1.838</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0634</v>
+        <v>1.0565</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1234</v>
+        <v>0.7815</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8069</v>
+        <v>-2.8047</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3741</v>
+        <v>-1.008</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4329</v>
+        <v>-1.7967</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1887</v>
+        <v>0.9435</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1887</v>
+        <v>0.9435</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3069</v>
+        <v>0.9234</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1176</v>
+        <v>0.5118</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1893</v>
+        <v>0.4115</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3018</v>
+        <v>-1.2452</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0251</v>
+        <v>-1.408</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6014</v>
+        <v>-1.1142</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4237</v>
+        <v>-0.2938</v>
       </c>
       <c r="G18" t="n">
         <v>-1.6185</v>
@@ -1858,13 +1858,13 @@
         <v>0.3774</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1422</v>
+        <v>0.4748</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.458</v>
+        <v>0.0292</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3157</v>
+        <v>0.4456</v>
       </c>
       <c r="V18" t="n">
         <v>1.2452</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.1549</v>
+        <v>-2.6918</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3199</v>
+        <v>-0.2224</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.835</v>
+        <v>-2.4693</v>
       </c>
       <c r="G19" t="n">
         <v>1.174</v>
@@ -1936,13 +1936,13 @@
         <v>0.7548</v>
       </c>
       <c r="S19" t="n">
-        <v>0.154</v>
+        <v>0.6171</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0617</v>
+        <v>0.1591</v>
       </c>
       <c r="U19" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.458</v>
       </c>
       <c r="V19" t="n">
         <v>-3.3507</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4142</v>
+        <v>-3.0786</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7975</v>
+        <v>-0.7000999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.6167</v>
+        <v>-2.3786</v>
       </c>
       <c r="G20" t="n">
         <v>-1.5931</v>
@@ -2014,13 +2014,13 @@
         <v>0.7548</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.3534</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3281</v>
+        <v>-0.2306</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3609</v>
+        <v>-0.1228</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9434</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.302</v>
+        <v>-5.083</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.349</v>
+        <v>-3.1541</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.953</v>
+        <v>-1.9289</v>
       </c>
       <c r="G21" t="n">
         <v>-5.5561</v>
@@ -2092,13 +2092,13 @@
         <v>0.9435</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6131</v>
+        <v>0.8321</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0987</v>
+        <v>0.2936</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5144</v>
+        <v>0.5385</v>
       </c>
       <c r="V21" t="n">
         <v>2.4714</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.682299999999999</v>
+        <v>-3.733499999999999</v>
       </c>
       <c r="E22" t="n">
         <v>9.4282</v>
       </c>
       <c r="F22" t="n">
-        <v>-15.1105</v>
+        <v>-13.1617</v>
       </c>
       <c r="G22" t="n">
         <v>-6.9322</v>
@@ -2170,13 +2170,13 @@
         <v>8.4915</v>
       </c>
       <c r="S22" t="n">
-        <v>4.779000000000001</v>
+        <v>6.7279</v>
       </c>
       <c r="T22" t="n">
-        <v>1.4514</v>
+        <v>1.4515</v>
       </c>
       <c r="U22" t="n">
-        <v>3.3276</v>
+        <v>5.2765</v>
       </c>
       <c r="V22" t="n">
         <v>3.075000000000001</v>
